--- a/output/quickfixpro_portfolio_daily.xlsx
+++ b/output/quickfixpro_portfolio_daily.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>618,562.63</t>
+          <t>281,066.87</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+518.56%</t>
+          <t>+181.07%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>648,246  (+548.25%)</t>
+          <t>287,979  (+187.98%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12,157  (29.7 pts of return)</t>
+          <t>4,087  (6.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8.44%</t>
+          <t>6.00%</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>61.4x</t>
+          <t>30.2x</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.86R  (best +9.50R)</t>
+          <t>+3.00R  (best +9.50R)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11,581  (+4.50%)</t>
+          <t>3,970  (+2.40%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-3,932  (-1.67%)</t>
+          <t>-1,420  (-0.91%)</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.9% of live balance</t>
+          <t>3.1% of live balance</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.573% of liquid capital</t>
+          <t>0.8% of liquid capital (solved for a 6% max drawdown)</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>100000</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1573</v>
+        <v>800</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,573)</t>
+          <t>Gold_Futures_COMEX short (risk 800)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -979,13 +979,13 @@
         <v>46010</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>105202.31</v>
+        <v>106472.28</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>105202.31</v>
+        <v>106472.28</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_bar (+5,202)</t>
+          <t>Gold_Futures_COMEX target_bar (+6,472)</t>
         </is>
       </c>
     </row>
@@ -1003,13 +1003,13 @@
         <v>46011</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>105202.31</v>
+        <v>106472.28</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>105202.31</v>
+        <v>106472.28</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>46021</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>105202.31</v>
+        <v>106472.28</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1654.83</v>
+        <v>851.78</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>103547.47</v>
+        <v>105620.5</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,655)</t>
+          <t>Gold_Futures_COMEX short (risk 852)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         <v>46023</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>105202.31</v>
+        <v>106472.28</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1654.83</v>
+        <v>851.78</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>103547.47</v>
+        <v>105620.5</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1075,13 +1075,13 @@
         <v>46024</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_bar (+3,244)</t>
+          <t>Gold_Futures_COMEX target_bar (+1,670)</t>
         </is>
       </c>
     </row>
@@ -1099,13 +1099,13 @@
         <v>46025</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1119,13 +1119,13 @@
         <v>46026</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1139,13 +1139,13 @@
         <v>46027</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1159,13 +1159,13 @@
         <v>46028</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>46029</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>108446.03</v>
+        <v>108141.9</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3384.88</v>
+        <v>1723.35</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>105061.15</v>
+        <v>106418.55</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures short (risk 1,706); S_P_500_Index short (risk 1,679)</t>
+          <t>Coffee_NYCSCE_Futures short (risk 865); S_P_500_Index short (risk 858)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1207,13 +1207,13 @@
         <v>46030</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,719); S_P_500_Index target_bar (+7,762)</t>
+          <t>Coffee_NYCSCE_Futures stop (-872); S_P_500_Index target_bar (+4,493)</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
         <v>46031</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1251,13 +1251,13 @@
         <v>46032</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>46033</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>46034</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>46035</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>114488.45</v>
+        <v>111763.35</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1800.9</v>
+        <v>894.11</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>112687.54</v>
+        <v>110869.24</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,801)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 894)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1339,13 +1339,13 @@
         <v>46036</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,954)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-970)</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>46037</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>46038</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1403,13 +1403,13 @@
         <v>46039</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>46040</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>46041</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1463,13 +1463,13 @@
         <v>46042</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>46043</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>112534.28</v>
+        <v>110793.14</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1770.16</v>
+        <v>886.35</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>110764.11</v>
+        <v>109906.8</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures long (risk 1,770)</t>
+          <t>Coffee_NYCSCE_Futures long (risk 886)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1511,13 +1511,13 @@
         <v>46044</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures target_bar (+1,653)</t>
+          <t>Coffee_NYCSCE_Futures target_bar (+827)</t>
         </is>
       </c>
     </row>
@@ -1535,13 +1535,13 @@
         <v>46045</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1555,13 +1555,13 @@
         <v>46046</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1575,13 +1575,13 @@
         <v>46047</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1595,13 +1595,13 @@
         <v>46048</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1615,13 +1615,13 @@
         <v>46049</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>114186.83</v>
+        <v>111620.6</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1796.16</v>
+        <v>892.96</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>112390.67</v>
+        <v>110727.63</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,796)</t>
+          <t>S_P_500_Index short (risk 893)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1643,13 +1643,13 @@
         <v>46050</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>112379.49</v>
+        <v>108893.11</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1767.91</v>
+        <v>885.8200000000001</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>110611.59</v>
+        <v>108007.29</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund short (risk 1,768)</t>
+          <t>Teucrium_Wheat_Fund short (risk 886)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,807)</t>
+          <t>S_P_500_Index stop (-2,727)</t>
         </is>
       </c>
     </row>
@@ -1675,13 +1675,13 @@
         <v>46051</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>110218.72</v>
+        <v>107761.19</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>5138.08</v>
+        <v>2571.49</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>105080.64</v>
+        <v>105189.69</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance long (risk 1,740); Live_Cattle_Futures_CME short (risk 1,713); S_P_500_Index short (risk 1,686)</t>
+          <t>Ethereum_Per_USD_Binance long (risk 864); Live_Cattle_Futures_CME short (risk 857); S_P_500_Index short (risk 850)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund stop (-2,161)</t>
+          <t>Teucrium_Wheat_Fund stop (-1,132)</t>
         </is>
       </c>
     </row>
@@ -1707,13 +1707,13 @@
         <v>46052</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>106544.01</v>
+        <v>105929.22</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>3338.53</v>
+        <v>1691.81</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>103205.48</v>
+        <v>104237.41</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,653)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 842)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,860); Live_Cattle_Futures_CME unknown_pl (-1,815)</t>
+          <t>Ethereum_Per_USD_Binance stop (-924); Live_Cattle_Futures_CME unknown_pl (-908)</t>
         </is>
       </c>
     </row>
@@ -1739,13 +1739,13 @@
         <v>46053</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>106544.01</v>
+        <v>105929.22</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>3338.53</v>
+        <v>1691.81</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>103205.48</v>
+        <v>104237.41</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -1763,13 +1763,13 @@
         <v>46054</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>106544.01</v>
+        <v>105929.22</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>3338.53</v>
+        <v>1691.81</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>103205.48</v>
+        <v>104237.41</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -1787,13 +1787,13 @@
         <v>46055</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>108142.62</v>
+        <v>106743.09</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>3309.04</v>
+        <v>1684.19</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>104833.59</v>
+        <v>105058.9</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,623)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 834)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures target_bar (+1,599)</t>
+          <t>Cocoa_NYCSCE_Futures target_bar (+814)</t>
         </is>
       </c>
     </row>
@@ -1819,13 +1819,13 @@
         <v>46056</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>104823.7</v>
+        <v>105053.88</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1649.03</v>
+        <v>840.47</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>103174.66</v>
+        <v>104213.41</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,649)</t>
+          <t>EURO_STOXX_50_Index short (risk 840)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,627); S_P_500_Index unknown_pl (-1,692)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-836); S_P_500_Index unknown_pl (-854)</t>
         </is>
       </c>
     </row>
@@ -1851,13 +1851,13 @@
         <v>46057</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>108676.71</v>
+        <v>107017.67</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>1622.94</v>
+        <v>833.71</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>107053.78</v>
+        <v>106183.96</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,623)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 834)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_bar (+3,853)</t>
+          <t>EURO_STOXX_50_Index target_bar (+1,964)</t>
         </is>
       </c>
     </row>
@@ -1883,13 +1883,13 @@
         <v>46058</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>108676.71</v>
+        <v>107017.67</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>3306.89</v>
+        <v>1683.18</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>105369.82</v>
+        <v>105334.49</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,684)</t>
+          <t>NY_Copper_Futures long (risk 849)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         <v>46059</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>106984.97</v>
+        <v>106164.27</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>3280.4</v>
+        <v>1676.38</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>103704.57</v>
+        <v>104487.88</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,657)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 843)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,692)</t>
+          <t>NY_Copper_Futures stop (-853)</t>
         </is>
       </c>
     </row>
@@ -1943,13 +1943,13 @@
         <v>46060</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>112852.27</v>
+        <v>109147.27</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1622.94</v>
+        <v>833.71</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>111229.33</v>
+        <v>108313.56</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -1962,7 +1962,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_bar (+5,867)</t>
+          <t>Bitcoin_Per_USD_Binance target_bar (+2,983)</t>
         </is>
       </c>
     </row>
@@ -1971,13 +1971,13 @@
         <v>46061</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>112852.27</v>
+        <v>109147.27</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>1622.94</v>
+        <v>833.71</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>111229.33</v>
+        <v>108313.56</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -1995,13 +1995,13 @@
         <v>46062</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>118385.02</v>
+        <v>111989.46</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>118385.02</v>
+        <v>111989.46</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -2010,7 +2010,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures target_bar (+5,533)</t>
+          <t>Cocoa_NYCSCE_Futures target_bar (+2,842)</t>
         </is>
       </c>
     </row>
@@ -2019,13 +2019,13 @@
         <v>46063</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>118385.02</v>
+        <v>111989.46</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>3695.1</v>
+        <v>1784.66</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>114689.92</v>
+        <v>110204.79</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,862); S_P_500_Index short (risk 1,833)</t>
+          <t>EURO_STOXX_50_Index short (risk 896); S_P_500_Index short (risk 889)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2047,13 +2047,13 @@
         <v>46064</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>118003.93</v>
+        <v>112006.98</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1804.07</v>
+        <v>881.64</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>116199.86</v>
+        <v>111125.34</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,804)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 882)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_bar (+1,468); S_P_500_Index unknown_pl (-1,849)</t>
+          <t>EURO_STOXX_50_Index target_bar (+914); S_P_500_Index unknown_pl (-897)</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46065</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>115951.02</v>
+        <v>111003.74</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1827.82</v>
+        <v>889</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>114123.2</v>
+        <v>110114.73</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,828)</t>
+          <t>EURO_STOXX_50_Index short (risk 889)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-2,053)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,003)</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         <v>46066</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>118609.75</v>
+        <v>112296.87</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1795.16</v>
+        <v>880.92</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>116814.59</v>
+        <v>111415.95</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,795)</t>
+          <t>NY_Copper_Futures long (risk 881)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_bar (+2,659)</t>
+          <t>EURO_STOXX_50_Index target_bar (+1,293)</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2143,13 @@
         <v>46067</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>118609.75</v>
+        <v>112296.87</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>1795.16</v>
+        <v>880.92</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>116814.59</v>
+        <v>111415.95</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -2167,13 +2167,13 @@
         <v>46068</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>118609.75</v>
+        <v>112296.87</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1795.16</v>
+        <v>880.92</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>116814.59</v>
+        <v>111415.95</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -2191,13 +2191,13 @@
         <v>46069</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>118609.75</v>
+        <v>112296.87</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1795.16</v>
+        <v>880.92</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>116814.59</v>
+        <v>111415.95</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -2215,13 +2215,13 @@
         <v>46070</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,803)</t>
+          <t>NY_Copper_Futures stop (-885)</t>
         </is>
       </c>
     </row>
@@ -2239,13 +2239,13 @@
         <v>46071</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2259,13 +2259,13 @@
         <v>46072</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2279,13 +2279,13 @@
         <v>46073</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2299,13 +2299,13 @@
         <v>46074</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2319,13 +2319,13 @@
         <v>46075</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2339,13 +2339,13 @@
         <v>46076</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1837.37</v>
+        <v>891.3</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>114969.58</v>
+        <v>110520.9</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,837)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 891)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2367,13 +2367,13 @@
         <v>46077</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>116806.95</v>
+        <v>111412.2</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>5425.87</v>
+        <v>2652.56</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>111381.08</v>
+        <v>108759.64</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,808); Ethereum_Per_USD_Binance long (risk 1,780)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 884); Ethereum_Per_USD_Binance long (risk 877)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         <v>46078</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>128770.51</v>
+        <v>117278.85</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>1837.37</v>
+        <v>891.3</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>126933.14</v>
+        <v>116387.55</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -2414,7 +2414,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures target_bar (+7,373); Ethereum_Per_USD_Binance target_bar (+4,591)</t>
+          <t>Cocoa_NYCSCE_Futures target_bar (+3,605); Ethereum_Per_USD_Binance target_bar (+2,262)</t>
         </is>
       </c>
     </row>
@@ -2423,13 +2423,13 @@
         <v>46079</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="C62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2438,7 +2438,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-2,362)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,146)</t>
         </is>
       </c>
     </row>
@@ -2447,13 +2447,13 @@
         <v>46080</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2467,13 +2467,13 @@
         <v>46081</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2487,13 +2487,13 @@
         <v>46082</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="C65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2507,13 +2507,13 @@
         <v>46083</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>126408.17</v>
+        <v>116132.89</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1988.4</v>
+        <v>929.0599999999999</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>124419.77</v>
+        <v>115203.83</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,988)</t>
+          <t>Gold_Futures_COMEX short (risk 929)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -2535,13 +2535,13 @@
         <v>46084</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>128631.74</v>
+        <v>117171.84</v>
       </c>
       <c r="C67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>128631.74</v>
+        <v>117171.84</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2550,7 +2550,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_bar (+2,224)</t>
+          <t>Gold_Futures_COMEX target_bar (+1,039)</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2559,13 @@
         <v>46085</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>128631.74</v>
+        <v>117171.84</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2023.38</v>
+        <v>937.37</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>126608.37</v>
+        <v>116234.46</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 2,023)</t>
+          <t>USD_EUR_Cross_Rate short (risk 937)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2587,13 +2587,13 @@
         <v>46086</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>126256.48</v>
+        <v>116071.44</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1991.55</v>
+        <v>929.88</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>124264.93</v>
+        <v>115141.57</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -2605,12 +2605,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>S_P_500_Index long (risk 1,992)</t>
+          <t>S_P_500_Index long (risk 930)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-2,375)</t>
+          <t>USD_EUR_Cross_Rate stop (-1,100)</t>
         </is>
       </c>
     </row>
@@ -2619,13 +2619,13 @@
         <v>46087</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>124261.55</v>
+        <v>115071.55</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>1954.69</v>
+        <v>921.13</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>122306.87</v>
+        <v>114150.42</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,955)</t>
+          <t>USD_EUR_Cross_Rate short (risk 921)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,995)</t>
+          <t>S_P_500_Index stop (-1,000)</t>
         </is>
       </c>
     </row>
@@ -2651,13 +2651,13 @@
         <v>46088</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>124261.55</v>
+        <v>115071.55</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>1954.69</v>
+        <v>921.13</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>122306.87</v>
+        <v>114150.42</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -2675,13 +2675,13 @@
         <v>46089</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>124261.55</v>
+        <v>115071.55</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>1954.69</v>
+        <v>921.13</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>122306.87</v>
+        <v>114150.42</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -2699,13 +2699,13 @@
         <v>46090</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2714,7 +2714,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate unknown_pl (-2,132)</t>
+          <t>USD_EUR_Cross_Rate target_bar (+209)</t>
         </is>
       </c>
     </row>
@@ -2723,13 +2723,13 @@
         <v>46091</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2743,13 +2743,13 @@
         <v>46092</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2763,13 +2763,13 @@
         <v>46093</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2783,13 +2783,13 @@
         <v>46094</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2803,13 +2803,13 @@
         <v>46095</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2823,13 +2823,13 @@
         <v>46096</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2843,13 +2843,13 @@
         <v>46097</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2863,13 +2863,13 @@
         <v>46098</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>122129.17</v>
+        <v>115280.88</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1921.09</v>
+        <v>922.25</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>120208.08</v>
+        <v>114358.63</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,921)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 922)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         <v>46099</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>127582.35</v>
+        <v>117898.75</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>127582.35</v>
+        <v>117898.75</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_bar (+5,453)</t>
+          <t>Bitcoin_Per_USD_Binance target_bar (+2,618)</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>46100</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>127582.35</v>
+        <v>117898.75</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>127582.35</v>
+        <v>117898.75</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2935,13 +2935,13 @@
         <v>46101</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>127582.35</v>
+        <v>117898.75</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>2006.87</v>
+        <v>943.1900000000001</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>125575.48</v>
+        <v>116955.56</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 2,007)</t>
+          <t>United_States_Oil_Fund_LP short (risk 943)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -2963,13 +2963,13 @@
         <v>46102</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>127582.35</v>
+        <v>117898.75</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>2006.87</v>
+        <v>943.1900000000001</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>125575.48</v>
+        <v>116955.56</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2987,13 +2987,13 @@
         <v>46103</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>127582.35</v>
+        <v>117898.75</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>2006.87</v>
+        <v>943.1900000000001</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>125575.48</v>
+        <v>116955.56</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -3011,13 +3011,13 @@
         <v>46104</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>132760.34</v>
+        <v>123953.87</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1975.3</v>
+        <v>935.64</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>130785.04</v>
+        <v>123018.23</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,975)</t>
+          <t>NY_Copper_Futures long (risk 936)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_bar (+5,178)</t>
+          <t>United_States_Oil_Fund_LP target_bar (+6,055)</t>
         </is>
       </c>
     </row>
@@ -3043,13 +3043,13 @@
         <v>46105</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>132760.34</v>
+        <v>123953.87</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>4032.55</v>
+        <v>1919.79</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>128727.79</v>
+        <v>122034.08</v>
       </c>
       <c r="E88" t="n">
         <v>2</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,057)</t>
+          <t>Gold_Futures_COMEX long (risk 984)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -3071,13 +3071,13 @@
         <v>46106</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -3086,7 +3086,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_bar (+10,750); NY_Copper_Futures target_bar (+7,960)</t>
+          <t>Gold_Futures_COMEX target_bar (+5,143); NY_Copper_Futures target_bar (+3,770)</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
         <v>46107</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -3115,13 +3115,13 @@
         <v>46108</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3135,13 +3135,13 @@
         <v>46109</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -3155,13 +3155,13 @@
         <v>46110</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -3175,13 +3175,13 @@
         <v>46111</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -3195,13 +3195,13 @@
         <v>46112</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>151470.56</v>
+        <v>132866.98</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>2382.63</v>
+        <v>1062.94</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>149087.92</v>
+        <v>131804.05</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 2,383)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,063)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -3223,13 +3223,13 @@
         <v>46113</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_bar (+18,175)</t>
+          <t>United_States_Oil_Fund_LP target_bar (+8,108)</t>
         </is>
       </c>
     </row>
@@ -3247,13 +3247,13 @@
         <v>46114</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -3267,13 +3267,13 @@
         <v>46115</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>46116</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -3307,13 +3307,13 @@
         <v>46117</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -3327,13 +3327,13 @@
         <v>46118</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -3347,13 +3347,13 @@
         <v>46119</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -3367,13 +3367,13 @@
         <v>46120</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
         <v>46121</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3407,13 +3407,13 @@
         <v>46122</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3427,13 +3427,13 @@
         <v>46123</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3447,13 +3447,13 @@
         <v>46124</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3467,13 +3467,13 @@
         <v>46125</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3487,13 +3487,13 @@
         <v>46126</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>169645.65</v>
+        <v>140975.23</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2668.53</v>
+        <v>1127.8</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>166977.12</v>
+        <v>139847.43</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 2,669)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 1,128)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -3515,13 +3515,13 @@
         <v>46127</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>172108.29</v>
+        <v>142016.01</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>7756.35</v>
+        <v>3329.56</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>164351.93</v>
+        <v>138686.45</v>
       </c>
       <c r="E110" t="n">
         <v>3</v>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance short (risk 2,627); Live_Cattle_Futures_CME short (risk 2,585); NY_Copper_Futures short (risk 2,545)</t>
+          <t>Ethereum_Per_USD_Binance short (risk 1,119); Live_Cattle_Futures_CME short (risk 1,110); NY_Copper_Futures short (risk 1,101)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_bar (+2,463)</t>
+          <t>Bitcoin_Per_USD_Binance target_bar (+1,041)</t>
         </is>
       </c>
     </row>
@@ -3547,13 +3547,13 @@
         <v>46128</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>199365.39</v>
+        <v>153689.17</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>199365.39</v>
+        <v>153689.17</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -3562,7 +3562,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_bar (+10,014); Live_Cattle_Futures_CME target_bar (+15,668); NY_Copper_Futures target_bar (+1,575)</t>
+          <t>Ethereum_Per_USD_Binance target_bar (+4,265); Live_Cattle_Futures_CME target_bar (+6,726); NY_Copper_Futures target_bar (+682)</t>
         </is>
       </c>
     </row>
@@ -3571,13 +3571,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -3585,12 +3585,12 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate long (risk 3,136)</t>
+          <t>USD_EUR_Cross_Rate long (risk 1,230)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate data_end (+2,934)</t>
+          <t>USD_EUR_Cross_Rate data_end (+1,150)</t>
         </is>
       </c>
     </row>
@@ -3599,13 +3599,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -3659,13 +3659,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>202299.08</v>
+        <v>154839.36</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>3182.16</v>
+        <v>1238.71</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>199116.91</v>
+        <v>153600.65</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 3,182)</t>
+          <t>Dow_Futures_E_mini short (risk 1,239)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -3687,13 +3687,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>219461.81</v>
+        <v>161520.26</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>219461.81</v>
+        <v>161520.26</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_bar (+17,163)</t>
+          <t>Dow_Futures_E_mini target_bar (+6,681)</t>
         </is>
       </c>
     </row>
@@ -3711,13 +3711,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>219461.81</v>
+        <v>161520.26</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>219461.81</v>
+        <v>161520.26</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3731,13 +3731,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>219461.81</v>
+        <v>161520.26</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>3452.13</v>
+        <v>1292.16</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>216009.67</v>
+        <v>160228.1</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 3,452)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 1,292)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3759,13 +3759,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>238242.4</v>
+        <v>168549.99</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>3397.83</v>
+        <v>1281.82</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>234844.57</v>
+        <v>167268.17</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 3,398)</t>
+          <t>S_P_500_E_mini short (risk 1,282)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_bar (+18,781)</t>
+          <t>Bitcoin_Per_USD_CME target_bar (+7,030)</t>
         </is>
       </c>
     </row>
@@ -3791,13 +3791,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>250501.79</v>
+        <v>173174.82</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>3694.11</v>
+        <v>1338.15</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>246807.68</v>
+        <v>171836.68</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,694)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,338)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini target_bar (+12,259)</t>
+          <t>S_P_500_E_mini target_bar (+4,625)</t>
         </is>
       </c>
     </row>
@@ -3823,13 +3823,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>254777.08</v>
+        <v>174723.49</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>3882.28</v>
+        <v>1374.69</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>250894.8</v>
+        <v>173348.8</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 3,882)</t>
+          <t>Corn_CBOT_Futures short (risk 1,375)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+4,275)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+1,549)</t>
         </is>
       </c>
     </row>
@@ -3855,13 +3855,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>250077.47</v>
+        <v>173059.39</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>11654.46</v>
+        <v>4127.18</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>238423.01</v>
+        <v>168932.21</v>
       </c>
       <c r="E123" t="n">
         <v>3</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 3,947); Live_Cattle_Futures_CME short (risk 3,884); US_Dollar_Index_Futures long (risk 3,823)</t>
+          <t>Japanese_Yen_Futures short (risk 1,387); Live_Cattle_Futures_CME short (risk 1,376); US_Dollar_Index_Futures long (risk 1,365)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-4,700)</t>
+          <t>Corn_CBOT_Futures stop (-1,664)</t>
         </is>
       </c>
     </row>
@@ -3887,13 +3887,13 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>262744.88</v>
+        <v>177558.15</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>7696.97</v>
+        <v>2738.25</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>255047.91</v>
+        <v>174819.9</v>
       </c>
       <c r="E124" t="n">
         <v>2</v>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 3,750)</t>
+          <t>Nasdaq_100_E_mini short (risk 1,351)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME target_bar (+8,142); US_Dollar_Index_Futures target_bar (+4,526)</t>
+          <t>Live_Cattle_Futures_CME target_bar (+2,883); US_Dollar_Index_Futures target_bar (+1,615)</t>
         </is>
       </c>
     </row>
@@ -3919,13 +3919,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>263098.53</v>
+        <v>177648.79</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>4011.9</v>
+        <v>1398.56</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>259086.62</v>
+        <v>176250.23</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 4,012)</t>
+          <t>Corn_CBOT_Futures short (risk 1,399)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures target_bar (+4,107); Nasdaq_100_E_mini stop (-3,753)</t>
+          <t>Japanese_Yen_Futures target_bar (+1,443); Nasdaq_100_E_mini stop (-1,352)</t>
         </is>
       </c>
     </row>
@@ -3951,13 +3951,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>296287.73</v>
+        <v>189218.63</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>8086.76</v>
+        <v>2808.72</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>288200.97</v>
+        <v>186409.9</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -3969,12 +3969,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 4,075); US_Dollar_Index_Futures long (risk 4,011)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 1,410); US_Dollar_Index_Futures long (risk 1,399)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures target_bar (+33,189)</t>
+          <t>Corn_CBOT_Futures target_bar (+11,570)</t>
         </is>
       </c>
     </row>
@@ -3983,13 +3983,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>308440.66</v>
+        <v>193423.25</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>13006.82</v>
+        <v>4369.35</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>295433.84</v>
+        <v>189053.9</v>
       </c>
       <c r="E127" t="n">
         <v>3</v>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 4,533); NY_Platinum_Futures short (risk 4,462)</t>
+          <t>EURO_Futures short (risk 1,491); NY_Platinum_Futures short (risk 1,479)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_bar (+12,153)</t>
+          <t>Bitcoin_Per_USD_CME target_bar (+4,205)</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4015,13 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>311780.06</v>
+        <v>194603.34</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>4011.33</v>
+        <v>1398.72</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>307768.74</v>
+        <v>193204.62</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
@@ -4034,7 +4034,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures unknown_pl (-4,650); NY_Platinum_Futures target_bar (+7,989)</t>
+          <t>EURO_Futures unknown_pl (-1,530); NY_Platinum_Futures target_bar (+2,710)</t>
         </is>
       </c>
     </row>
@@ -4043,13 +4043,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>311780.06</v>
+        <v>194603.34</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>8852.530000000001</v>
+        <v>2944.36</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>302927.53</v>
+        <v>191658.99</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 4,841)</t>
+          <t>Gold_Futures_COMEX short (risk 1,546)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -4071,13 +4071,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>314888.57</v>
+        <v>195834.28</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>4765.05</v>
+        <v>1533.27</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>310123.52</v>
+        <v>194301</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 4,765)</t>
+          <t>Silver_Futures_COMEX short (risk 1,533)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX unknown_pl (-4,996); US_Dollar_Index_Futures target_bar (+8,105)</t>
+          <t>Gold_Futures_COMEX unknown_pl (-1,595); US_Dollar_Index_Futures target_bar (+2,826)</t>
         </is>
       </c>
     </row>
@@ -4103,13 +4103,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>310113.6</v>
+        <v>194297.81</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>310113.6</v>
+        <v>194297.81</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4118,7 +4118,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-4,775)</t>
+          <t>Silver_Futures_COMEX stop (-1,536)</t>
         </is>
       </c>
     </row>
@@ -4127,13 +4127,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>310113.6</v>
+        <v>194297.81</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>4878.09</v>
+        <v>1554.38</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>305235.51</v>
+        <v>192743.43</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,878)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,554)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4155,13 +4155,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -4170,7 +4170,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+20,515)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+6,537)</t>
         </is>
       </c>
     </row>
@@ -4179,13 +4179,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -4199,13 +4199,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -4219,13 +4219,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>5200.78</v>
+        <v>1606.68</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>325427.62</v>
+        <v>199228.09</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 5,201)</t>
+          <t>US_Dollar_Index_Futures short (risk 1,607)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4247,13 +4247,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>330628.4</v>
+        <v>200834.77</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>10319.76</v>
+        <v>3200.5</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>320308.64</v>
+        <v>197634.27</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 5,119)</t>
+          <t>NY_Palladium_Futures long (risk 1,594)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4275,13 +4275,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>344329.01</v>
+        <v>205100.54</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>5200.78</v>
+        <v>1606.68</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>339128.23</v>
+        <v>203493.86</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -4294,7 +4294,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures target_bar (+13,701)</t>
+          <t>NY_Palladium_Futures target_bar (+4,266)</t>
         </is>
       </c>
     </row>
@@ -4303,13 +4303,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>357664.57</v>
+        <v>209220.29</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>357664.57</v>
+        <v>209220.29</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures target_bar (+13,336)</t>
+          <t>US_Dollar_Index_Futures target_bar (+4,120)</t>
         </is>
       </c>
     </row>
@@ -4327,13 +4327,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>357664.57</v>
+        <v>209220.29</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>357664.57</v>
+        <v>209220.29</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -4347,13 +4347,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>357664.57</v>
+        <v>209220.29</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>357664.57</v>
+        <v>209220.29</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -4367,13 +4367,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>357664.57</v>
+        <v>209220.29</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>11163.63</v>
+        <v>3334.13</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>346500.94</v>
+        <v>205886.16</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 5,626); US_Dollar_Index_Futures short (risk 5,538)</t>
+          <t>Silver_Futures_COMEX long (risk 1,674); US_Dollar_Index_Futures short (risk 1,660)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4395,13 +4395,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>365150.7</v>
+        <v>211447.43</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>5537.57</v>
+        <v>1660.37</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>359613.14</v>
+        <v>209787.05</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
@@ -4414,7 +4414,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX target_bar (+7,486)</t>
+          <t>Silver_Futures_COMEX target_bar (+2,227)</t>
         </is>
       </c>
     </row>
@@ -4423,13 +4423,13 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>365150.7</v>
+        <v>211447.43</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>5537.57</v>
+        <v>1660.37</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>359613.14</v>
+        <v>209787.05</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -4447,13 +4447,13 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>359526.27</v>
+        <v>209761.01</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>359526.27</v>
+        <v>209761.01</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4462,7 +4462,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-5,624)</t>
+          <t>US_Dollar_Index_Futures stop (-1,686)</t>
         </is>
       </c>
     </row>
@@ -4471,13 +4471,13 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>359526.27</v>
+        <v>209761.01</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>359526.27</v>
+        <v>209761.01</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -4491,13 +4491,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>359526.27</v>
+        <v>209761.01</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>5655.35</v>
+        <v>1678.09</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>353870.92</v>
+        <v>208082.92</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 5,655)</t>
+          <t>Dow_Futures_E_mini short (risk 1,678)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -4519,13 +4519,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>413252.26</v>
+        <v>225702.9</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>11045.22</v>
+        <v>3316.01</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>402207.04</v>
+        <v>222386.89</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 5,566); US_Dollar_Index_Futures short (risk 5,479)</t>
+          <t>Gold_Futures_COMEX long (risk 1,665); US_Dollar_Index_Futures short (risk 1,651)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_bar (+53,726)</t>
+          <t>Dow_Futures_E_mini target_bar (+15,942)</t>
         </is>
       </c>
     </row>
@@ -4551,13 +4551,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>418196.31</v>
+        <v>227206.23</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>418196.31</v>
+        <v>227206.23</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4566,7 +4566,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX unknown_pl (-5,608); US_Dollar_Index_Futures target_bar (+10,552)</t>
+          <t>Gold_Futures_COMEX unknown_pl (-1,677); US_Dollar_Index_Futures target_bar (+3,180)</t>
         </is>
       </c>
     </row>
@@ -4575,13 +4575,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>418196.31</v>
+        <v>227206.23</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>418196.31</v>
+        <v>227206.23</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4595,13 +4595,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>418196.31</v>
+        <v>227206.23</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>13052.98</v>
+        <v>3620.76</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>405143.33</v>
+        <v>223585.47</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 6,578); US_Dollar_Index_Futures short (risk 6,475)</t>
+          <t>Gold_Futures_COMEX long (risk 1,818); US_Dollar_Index_Futures short (risk 1,803)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -4623,13 +4623,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>447122.92</v>
+        <v>235977.22</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>6372.9</v>
+        <v>1788.68</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>440750.02</v>
+        <v>234188.54</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4641,12 +4641,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 6,373)</t>
+          <t>Corn_CBOT_Futures long (risk 1,789)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_bar (+15,977); US_Dollar_Index_Futures target_bar (+12,950)</t>
+          <t>Gold_Futures_COMEX target_bar (+4,415); US_Dollar_Index_Futures target_bar (+4,356)</t>
         </is>
       </c>
     </row>
@@ -4655,13 +4655,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>439805.88</v>
+        <v>233923.55</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>6933</v>
+        <v>1873.51</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>432872.88</v>
+        <v>232050.04</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4673,12 +4673,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 6,933)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 1,874)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-7,317)</t>
+          <t>Corn_CBOT_Futures stop (-2,054)</t>
         </is>
       </c>
     </row>
@@ -4687,13 +4687,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>453881.93</v>
+        <v>237727.33</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>453881.93</v>
+        <v>237727.33</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+14,076)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+3,804)</t>
         </is>
       </c>
     </row>
@@ -4711,13 +4711,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>453881.93</v>
+        <v>237727.33</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>7139.56</v>
+        <v>1901.82</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>446742.36</v>
+        <v>235825.51</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 7,140)</t>
+          <t>US_Dollar_Index_Futures short (risk 1,902)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -4739,13 +4739,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>446645.56</v>
+        <v>235799.72</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>446645.56</v>
+        <v>235799.72</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4754,7 +4754,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-7,236)</t>
+          <t>US_Dollar_Index_Futures stop (-1,928)</t>
         </is>
       </c>
     </row>
@@ -4763,13 +4763,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>446645.56</v>
+        <v>235799.72</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>7025.73</v>
+        <v>1886.4</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>439619.82</v>
+        <v>233913.32</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 7,026)</t>
+          <t>US_Dollar_Index_Futures short (risk 1,886)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -4791,13 +4791,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>446645.56</v>
+        <v>235799.72</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>7025.73</v>
+        <v>1886.4</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>439619.82</v>
+        <v>233913.32</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
@@ -4815,13 +4815,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>439522.91</v>
+        <v>233887.3</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>6915.22</v>
+        <v>1871.31</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>432607.7</v>
+        <v>232016</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 6,915)</t>
+          <t>NY_Platinum_Futures long (risk 1,871)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-7,123)</t>
+          <t>US_Dollar_Index_Futures stop (-1,912)</t>
         </is>
       </c>
     </row>
@@ -4847,13 +4847,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>432472.76</v>
+        <v>231979.48</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>6804.92</v>
+        <v>1856.13</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>425667.85</v>
+        <v>230123.36</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -4865,12 +4865,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 6,805)</t>
+          <t>EURO_Futures long (risk 1,856)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-7,050)</t>
+          <t>NY_Platinum_Futures stop (-1,908)</t>
         </is>
       </c>
     </row>
@@ -4879,13 +4879,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>440214.4</v>
+        <v>234091.11</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>26157.68</v>
+        <v>7276.05</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>414056.73</v>
+        <v>226815.06</v>
       </c>
       <c r="E161" t="n">
         <v>4</v>
@@ -4897,12 +4897,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 6,696); NY_Palladium_Futures long (risk 6,590); NY_Platinum_Futures long (risk 6,487); US_Dollar_Index_Futures short (risk 6,385)</t>
+          <t>NY_Natural_Gas_Futures short (risk 1,841); NY_Palladium_Futures long (risk 1,826); NY_Platinum_Futures long (risk 1,812); US_Dollar_Index_Futures short (risk 1,797)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>EURO_Futures target_bar (+7,742)</t>
+          <t>EURO_Futures target_bar (+2,112)</t>
         </is>
       </c>
     </row>
@@ -4911,13 +4911,13 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>492769.37</v>
+        <v>249067.81</v>
       </c>
       <c r="C162" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>492769.37</v>
+        <v>249067.81</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-7,242); NY_Palladium_Futures target_bar (+35,467); NY_Platinum_Futures target_bar (+6,009); US_Dollar_Index_Futures target_bar (+18,322)</t>
+          <t>NY_Natural_Gas_Futures stop (-1,991); NY_Palladium_Futures target_bar (+9,828); NY_Platinum_Futures target_bar (+1,983); US_Dollar_Index_Futures target_bar (+5,157)</t>
         </is>
       </c>
     </row>
@@ -4935,13 +4935,13 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>492769.37</v>
+        <v>249067.81</v>
       </c>
       <c r="C163" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>492769.37</v>
+        <v>249067.81</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4955,13 +4955,13 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>492769.37</v>
+        <v>249067.81</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>22889.92</v>
+        <v>5929.93</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>469879.45</v>
+        <v>243137.88</v>
       </c>
       <c r="E164" t="n">
         <v>3</v>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 7,751); German_Long_Bund short (risk 7,629); Gold_Futures_COMEX long (risk 7,509)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 1,993); German_Long_Bund short (risk 1,977); Gold_Futures_COMEX long (risk 1,961)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -4983,13 +4983,13 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>558509.76</v>
+        <v>266258.81</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>21826.65</v>
+        <v>5788.75</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>536683.11</v>
+        <v>260470.06</v>
       </c>
       <c r="E165" t="n">
         <v>3</v>
@@ -5001,12 +5001,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 7,391); NY_Platinum_Futures long (risk 7,275); Sugar_World_CSCE_Futures short (risk 7,161)</t>
+          <t>Dow_Futures_E_mini short (risk 1,945); NY_Platinum_Futures long (risk 1,930); Sugar_World_CSCE_Futures short (risk 1,914)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+31,194); German_Long_Bund target_bar (+9,951); Gold_Futures_COMEX target_bar (+24,595)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+8,019); German_Long_Bund target_bar (+2,750); Gold_Futures_COMEX target_bar (+6,422)</t>
         </is>
       </c>
     </row>
@@ -5015,13 +5015,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>577703.53</v>
+        <v>271373.64</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>577703.53</v>
+        <v>271373.64</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -5030,7 +5030,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-7,471); NY_Platinum_Futures target_bar (+22,534); Sugar_World_CSCE_Futures target_bar (+4,131)</t>
+          <t>Dow_Futures_E_mini stop (-1,966); NY_Platinum_Futures target_bar (+5,977); Sugar_World_CSCE_Futures target_bar (+1,104)</t>
         </is>
       </c>
     </row>
@@ -5039,13 +5039,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>577703.53</v>
+        <v>271373.64</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>577703.53</v>
+        <v>271373.64</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -5059,13 +5059,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>577703.53</v>
+        <v>271373.64</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>577703.53</v>
+        <v>271373.64</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -5079,13 +5079,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>577703.53</v>
+        <v>271373.64</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>18031.61</v>
+        <v>4324.61</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>559671.92</v>
+        <v>267049.03</v>
       </c>
       <c r="E169" t="n">
         <v>2</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 9,087); NY_Natural_Gas_Futures short (risk 8,944)</t>
+          <t>Live_Cattle_Futures_CME long (risk 2,171); NY_Natural_Gas_Futures short (risk 2,154)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -5107,13 +5107,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>595416.74</v>
+        <v>275638.64</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>9087.280000000001</v>
+        <v>2170.99</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>586329.47</v>
+        <v>273467.65</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
@@ -5126,7 +5126,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures target_bar (+17,713)</t>
+          <t>NY_Natural_Gas_Futures target_bar (+4,265)</t>
         </is>
       </c>
     </row>
@@ -5135,13 +5135,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>585896.74</v>
+        <v>273364.27</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>585896.74</v>
+        <v>273364.27</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -5150,7 +5150,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME stop (-9,520)</t>
+          <t>Live_Cattle_Futures_CME stop (-2,274)</t>
         </is>
       </c>
     </row>
@@ -5159,13 +5159,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>585896.74</v>
+        <v>273364.27</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>9216.16</v>
+        <v>2186.91</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>576680.58</v>
+        <v>271177.36</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 9,216)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,187)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5187,13 +5187,13 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>598981</v>
+        <v>276469.05</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>598981</v>
+        <v>276469.05</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -5202,7 +5202,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+13,084)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_bar (+3,105)</t>
         </is>
       </c>
     </row>
@@ -5211,13 +5211,13 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>598981</v>
+        <v>276469.05</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>598981</v>
+        <v>276469.05</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -5231,13 +5231,13 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>598981</v>
+        <v>276469.05</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>598981</v>
+        <v>276469.05</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -5251,13 +5251,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>598981</v>
+        <v>276469.05</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>9421.969999999999</v>
+        <v>2211.75</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>589559.02</v>
+        <v>274257.3</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 9,422)</t>
+          <t>Gold_Futures_COMEX long (risk 2,212)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -5279,13 +5279,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_bar (+20,005)</t>
+          <t>Gold_Futures_COMEX target_bar (+4,696)</t>
         </is>
       </c>
     </row>
@@ -5303,13 +5303,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -5323,13 +5323,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -5343,13 +5343,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>281165.09</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -5363,13 +5363,13 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>618562.63</v>
+        <v>281066.87</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>618562.63</v>
+        <v>281066.87</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 9,737); Corn_CBOT_Futures short (risk 9,583)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,249); Corn_CBOT_Futures short (risk 2,231)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -5508,25 +5508,25 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3.319</v>
+        <v>8.102</v>
       </c>
       <c r="G2" t="n">
         <v>0.012</v>
       </c>
       <c r="H2" t="n">
-        <v>3.307</v>
+        <v>8.09</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>100000</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>1573</v>
+        <v>1175</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>5202.31</v>
+        <v>9506.16</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>105202.31</v>
+        <v>109506.16</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5568,16 +5568,16 @@
         <v>1.96</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>105202.31</v>
+        <v>109506.16</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>1654.83</v>
+        <v>1286.7</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>3243.73</v>
+        <v>2522.12</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>108446.03</v>
+        <v>112028.29</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5619,16 +5619,16 @@
         <v>-1.008</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>108446.03</v>
+        <v>112028.29</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1705.86</v>
+        <v>1316.33</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-1719.34</v>
+        <v>-1326.74</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>106726.69</v>
+        <v>110701.55</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5661,25 +5661,25 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4.625</v>
+        <v>5.238</v>
       </c>
       <c r="G5" t="n">
         <v>0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>4.623</v>
+        <v>5.236</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>106740.18</v>
+        <v>110711.96</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1679.02</v>
+        <v>1300.87</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>7761.76</v>
+        <v>6811.05</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>114488.45</v>
+        <v>117512.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5721,16 +5721,16 @@
         <v>-1.085</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>114488.45</v>
+        <v>117512.6</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1800.9</v>
+        <v>1380.77</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>-1954.17</v>
+        <v>-1498.29</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>112534.28</v>
+        <v>116014.31</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -5772,16 +5772,16 @@
         <v>0.9340000000000001</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>112534.28</v>
+        <v>116014.31</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1770.16</v>
+        <v>1363.17</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1652.55</v>
+        <v>1272.6</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>114186.83</v>
+        <v>117286.91</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -5814,25 +5814,25 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
+        <v>-3.048</v>
       </c>
       <c r="G8" t="n">
         <v>0.006</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.006</v>
+        <v>-3.054</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>114186.83</v>
+        <v>117286.91</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1796.16</v>
+        <v>1378.12</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-1807.33</v>
+        <v>-4209.36</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>112379.49</v>
+        <v>113077.55</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -5865,25 +5865,25 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>-1</v>
+        <v>-1.056</v>
       </c>
       <c r="G9" t="n">
         <v>0.222</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.222</v>
+        <v>-1.278</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>112390.67</v>
+        <v>115908.79</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1767.91</v>
+        <v>1361.93</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-2160.77</v>
+        <v>-1740.3</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>110218.72</v>
+        <v>111337.24</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -5925,16 +5925,16 @@
         <v>-1.069</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>110611.59</v>
+        <v>111715.62</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1739.92</v>
+        <v>1312.66</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-1859.91</v>
+        <v>-1403.19</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>108358.81</v>
+        <v>109934.06</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -5976,16 +5976,16 @@
         <v>-1.06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>108871.67</v>
+        <v>110402.96</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1712.55</v>
+        <v>1297.23</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-1814.79</v>
+        <v>-1374.68</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>106544.01</v>
+        <v>108559.38</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -6027,16 +6027,16 @@
         <v>-1.004</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>107159.12</v>
+        <v>109105.72</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1685.61</v>
+        <v>1281.99</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>-1692.07</v>
+        <v>-1286.9</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>104823.7</v>
+        <v>107245.16</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6078,16 +6078,16 @@
         <v>0.967</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>105080.64</v>
+        <v>107445.36</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1652.92</v>
+        <v>1262.48</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1598.61</v>
+        <v>1221</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>108142.62</v>
+        <v>109780.38</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -6129,16 +6129,16 @@
         <v>-1.002</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>103205.48</v>
+        <v>106014.9</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1623.42</v>
+        <v>1245.68</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1626.86</v>
+        <v>-1248.31</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>106515.76</v>
+        <v>108532.06</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6180,16 +6180,16 @@
         <v>2.337</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>104833.59</v>
+        <v>107252.71</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1649.03</v>
+        <v>1260.22</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>3853.02</v>
+        <v>2944.54</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>108676.71</v>
+        <v>110189.71</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -6231,16 +6231,16 @@
         <v>3.409</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>103174.66</v>
+        <v>105984.95</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1622.94</v>
+        <v>1245.32</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>5532.75</v>
+        <v>4245.43</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>118385.02</v>
+        <v>117627.31</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>-1.005</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>107053.78</v>
+        <v>108944.38</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1683.96</v>
+        <v>1280.1</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>-1691.74</v>
+        <v>-1286.02</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>106984.97</v>
+        <v>108903.69</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -6333,16 +6333,16 @@
         <v>3.54</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>105369.82</v>
+        <v>107664.29</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1657.47</v>
+        <v>1265.06</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>5867.3</v>
+        <v>4478.19</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>112852.27</v>
+        <v>113381.88</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6375,25 +6375,25 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.79</v>
+        <v>1.022</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.788</v>
+        <v>1.02</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>118385.02</v>
+        <v>117627.31</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1862.2</v>
+        <v>1382.12</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1468.33</v>
+        <v>1410.44</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>119853.35</v>
+        <v>119037.76</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>-1.009</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>116522.82</v>
+        <v>116245.19</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1832.9</v>
+        <v>1365.88</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-1849.42</v>
+        <v>-1378.19</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>118003.93</v>
+        <v>117659.57</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -6486,16 +6486,16 @@
         <v>-1.138</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>114689.92</v>
+        <v>114879.31</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1804.07</v>
+        <v>1349.83</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-2052.91</v>
+        <v>-1536.02</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>115951.02</v>
+        <v>116123.55</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6537,16 +6537,16 @@
         <v>1.455</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>116199.86</v>
+        <v>116309.74</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1827.82</v>
+        <v>1366.64</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>2658.73</v>
+        <v>1987.89</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>118609.75</v>
+        <v>118111.45</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6588,16 +6588,16 @@
         <v>-1.004</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>114123.2</v>
+        <v>114756.91</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>1795.16</v>
+        <v>1348.39</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-1802.8</v>
+        <v>-1354.13</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>116806.95</v>
+        <v>116757.32</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6639,16 +6639,16 @@
         <v>-1.286</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>116806.95</v>
+        <v>116757.32</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1837.37</v>
+        <v>1371.9</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>-2362.34</v>
+        <v>-1763.87</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>126408.17</v>
+        <v>123976.23</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6690,16 +6690,16 @@
         <v>4.077</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>114969.58</v>
+        <v>115385.42</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1808.47</v>
+        <v>1355.78</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>7372.99</v>
+        <v>5527.4</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>124179.94</v>
+        <v>122284.71</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -6741,16 +6741,16 @@
         <v>2.579</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>113161.11</v>
+        <v>114029.64</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1780.02</v>
+        <v>1339.85</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>4590.57</v>
+        <v>3455.38</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>128770.51</v>
+        <v>125740.1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -6792,16 +6792,16 @@
         <v>1.118</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>126408.17</v>
+        <v>123976.23</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>1988.4</v>
+        <v>1456.72</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>2223.57</v>
+        <v>1629.01</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>128631.74</v>
+        <v>125605.24</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -6843,16 +6843,16 @@
         <v>-1.174</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>128631.74</v>
+        <v>125605.24</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>2023.38</v>
+        <v>1475.86</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-2375.27</v>
+        <v>-1732.53</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>126256.48</v>
+        <v>123872.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -6885,25 +6885,25 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>-1</v>
+        <v>-1.074</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.002</v>
+        <v>-1.075</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>126608.37</v>
+        <v>124129.38</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1991.55</v>
+        <v>1458.52</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>-1994.92</v>
+        <v>-1568.34</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>124261.55</v>
+        <v>122304.37</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -6936,29 +6936,29 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>-1</v>
+        <v>0.273</v>
       </c>
       <c r="G30" t="n">
-        <v>0.091</v>
+        <v>0.045</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.091</v>
+        <v>0.227</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>124264.93</v>
+        <v>122414.18</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>1954.69</v>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-2132.39</v>
+        <v>1438.37</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>326.86</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>122129.17</v>
+        <v>122631.23</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_bar</t>
         </is>
       </c>
     </row>
@@ -6996,16 +6996,16 @@
         <v>2.839</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>122129.17</v>
+        <v>122631.23</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1921.09</v>
+        <v>1440.92</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>5453.18</v>
+        <v>4090.16</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>127582.35</v>
+        <v>126721.39</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -7038,25 +7038,25 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>2.595</v>
+        <v>6.435</v>
       </c>
       <c r="G32" t="n">
         <v>0.015</v>
       </c>
       <c r="H32" t="n">
-        <v>2.58</v>
+        <v>6.42</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>127582.35</v>
+        <v>126721.39</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>2006.87</v>
+        <v>1488.98</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>5177.99</v>
+        <v>9558.98</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>132760.34</v>
+        <v>136280.37</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7098,16 +7098,16 @@
         <v>4.03</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>125575.48</v>
+        <v>125232.42</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1975.3</v>
+        <v>1471.48</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>7959.74</v>
+        <v>5929.53</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>151470.56</v>
+        <v>150487.36</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -7149,16 +7149,16 @@
         <v>5.226</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>130785.04</v>
+        <v>134808.89</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>2057.25</v>
+        <v>1584</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>10750.47</v>
+        <v>8277.459999999999</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>143510.81</v>
+        <v>144557.84</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -7200,16 +7200,16 @@
         <v>7.628</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>151470.56</v>
+        <v>150487.36</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>2382.63</v>
+        <v>1768.23</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>18175.09</v>
+        <v>13488.31</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>169645.65</v>
+        <v>163975.68</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -7251,16 +7251,16 @@
         <v>0.923</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>169645.65</v>
+        <v>163975.68</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>2668.53</v>
+        <v>1926.71</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>2462.64</v>
+        <v>1778.06</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>172108.29</v>
+        <v>165753.74</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -7302,16 +7302,16 @@
         <v>3.812</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>166977.12</v>
+        <v>162048.96</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>2626.55</v>
+        <v>1904.08</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>10013.72</v>
+        <v>7259.29</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>182122.01</v>
+        <v>173013.02</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7353,16 +7353,16 @@
         <v>6.061</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>164350.57</v>
+        <v>160144.89</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2585.23</v>
+        <v>1881.7</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>15668.06</v>
+        <v>11404.23</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>197790.07</v>
+        <v>184417.26</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -7404,16 +7404,16 @@
         <v>0.619</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>161765.34</v>
+        <v>158263.18</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>2544.57</v>
+        <v>1859.59</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>1575.32</v>
+        <v>1151.26</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>199365.39</v>
+        <v>185568.51</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>199365.39</v>
+        <v>185568.51</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>3136.02</v>
+        <v>2180.43</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2933.69</v>
+        <v>2039.76</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>202299.08</v>
+        <v>187608.27</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -7506,16 +7506,16 @@
         <v>5.393</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>202299.08</v>
+        <v>187608.27</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>3182.16</v>
+        <v>2204.4</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>17162.73</v>
+        <v>11889.22</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>219461.81</v>
+        <v>199497.49</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7557,16 +7557,16 @@
         <v>5.44</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>219461.81</v>
+        <v>199497.49</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>3452.13</v>
+        <v>2344.1</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>18780.59</v>
+        <v>12752.55</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>238242.4</v>
+        <v>212250.04</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7608,16 +7608,16 @@
         <v>3.608</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>216009.67</v>
+        <v>197153.4</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>3397.83</v>
+        <v>2316.55</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>12259.39</v>
+        <v>8358.129999999999</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>250501.79</v>
+        <v>220608.17</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7659,16 +7659,16 @@
         <v>1.157</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>234844.57</v>
+        <v>209933.49</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>3694.11</v>
+        <v>2466.72</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>4275.29</v>
+        <v>2854.8</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>254777.08</v>
+        <v>223462.97</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7710,16 +7710,16 @@
         <v>-1.211</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>246807.68</v>
+        <v>218141.45</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>3882.28</v>
+        <v>2563.16</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>-4699.61</v>
+        <v>-3102.78</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>250077.47</v>
+        <v>220360.2</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -7761,16 +7761,16 @@
         <v>1.041</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>250894.8</v>
+        <v>220899.81</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>3946.58</v>
+        <v>2595.57</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>4106.59</v>
+        <v>2700.81</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>266851.48</v>
+        <v>231437.85</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -7812,16 +7812,16 @@
         <v>2.096</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>246948.22</v>
+        <v>218304.24</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>3884.5</v>
+        <v>2565.07</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>8141.9</v>
+        <v>5376.4</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>258219.38</v>
+        <v>225736.59</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -7863,16 +7863,16 @@
         <v>1.184</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>243063.72</v>
+        <v>215739.16</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>3823.39</v>
+        <v>2534.94</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>4525.51</v>
+        <v>3000.44</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>262744.88</v>
+        <v>228737.04</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -7914,16 +7914,16 @@
         <v>-1.001</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>238423.01</v>
+        <v>212664.61</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>3750.39</v>
+        <v>2498.81</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>-3752.95</v>
+        <v>-2500.51</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>263098.53</v>
+        <v>228937.34</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -7965,16 +7965,16 @@
         <v>8.273</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>255047.91</v>
+        <v>223642.65</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>4011.9</v>
+        <v>2627.8</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>33189.2</v>
+        <v>21738.96</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>296287.73</v>
+        <v>250676.3</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8016,16 +8016,16 @@
         <v>2.982</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>259086.62</v>
+        <v>226309.54</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>4075.43</v>
+        <v>2659.14</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>12152.93</v>
+        <v>7929.54</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>308440.66</v>
+        <v>258605.84</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8067,16 +8067,16 @@
         <v>2.02</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>255011.19</v>
+        <v>223650.4</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>4011.33</v>
+        <v>2627.89</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>8104.63</v>
+        <v>5309.49</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>314888.57</v>
+        <v>263045.78</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8118,16 +8118,16 @@
         <v>-1.026</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>288200.97</v>
+        <v>245389.27</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>4533.4</v>
+        <v>2883.32</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>-4649.64</v>
+        <v>-2957.26</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>303791.01</v>
+        <v>255648.58</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8160,25 +8160,25 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1.797</v>
+        <v>1.839</v>
       </c>
       <c r="G54" t="n">
         <v>0.007</v>
       </c>
       <c r="H54" t="n">
-        <v>1.79</v>
+        <v>1.832</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>283667.57</v>
+        <v>242505.95</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>4462.09</v>
+        <v>2849.44</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>7989.05</v>
+        <v>5219.12</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>311780.06</v>
+        <v>260867.7</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8220,16 +8220,16 @@
         <v>-1.032</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>307768.74</v>
+        <v>258239.81</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>4841.2</v>
+        <v>3034.32</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>-4996.12</v>
+        <v>-3131.42</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>306783.94</v>
+        <v>257736.29</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -8271,16 +8271,16 @@
         <v>-1.002</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>302927.53</v>
+        <v>255205.49</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>4765.05</v>
+        <v>2998.66</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-4774.98</v>
+        <v>-3004.91</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>310113.6</v>
+        <v>260040.87</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8322,16 +8322,16 @@
         <v>4.206</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>310113.6</v>
+        <v>260040.87</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>4878.09</v>
+        <v>3055.48</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>20514.81</v>
+        <v>12849.83</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>330628.4</v>
+        <v>272890.7</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8373,16 +8373,16 @@
         <v>2.564</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>330628.4</v>
+        <v>272890.7</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>5200.78</v>
+        <v>3206.47</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>13335.56</v>
+        <v>8221.84</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>357664.57</v>
+        <v>289593.6</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -8424,16 +8424,16 @@
         <v>2.676</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>325427.62</v>
+        <v>269684.23</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>5118.98</v>
+        <v>3168.79</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>13700.61</v>
+        <v>8481.059999999999</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>344329.01</v>
+        <v>281371.76</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8475,16 +8475,16 @@
         <v>1.331</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>357664.57</v>
+        <v>289593.6</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>5626.06</v>
+        <v>3402.72</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>7486.13</v>
+        <v>4527.72</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>365150.7</v>
+        <v>294121.32</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8526,16 +8526,16 @@
         <v>-1.016</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>352038.51</v>
+        <v>286190.87</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>5537.57</v>
+        <v>3362.74</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-5624.43</v>
+        <v>-3415.49</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>359526.27</v>
+        <v>290705.82</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8577,16 +8577,16 @@
         <v>9.5</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>359526.27</v>
+        <v>290705.82</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>5655.35</v>
+        <v>3415.79</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>53725.99</v>
+        <v>32450.15</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>413252.26</v>
+        <v>323155.97</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8628,16 +8628,16 @@
         <v>-1.007</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>353870.92</v>
+        <v>287290.03</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>5566.39</v>
+        <v>3375.66</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>-5607.55</v>
+        <v>-3400.62</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>407644.72</v>
+        <v>319755.36</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8679,16 +8679,16 @@
         <v>1.926</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>348304.53</v>
+        <v>283914.37</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>5478.83</v>
+        <v>3335.99</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>10551.6</v>
+        <v>6424.74</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>418196.31</v>
+        <v>326180.1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -8730,16 +8730,16 @@
         <v>2.429</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>418196.31</v>
+        <v>326180.1</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>6578.23</v>
+        <v>3832.62</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>15977.1</v>
+        <v>9308.6</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>434173.42</v>
+        <v>335488.7</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -8772,25 +8772,25 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>2.008</v>
+        <v>2.424</v>
       </c>
       <c r="G66" t="n">
         <v>0.008</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>2.416</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>411618.09</v>
+        <v>322347.48</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>6474.75</v>
+        <v>3787.58</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>12949.5</v>
+        <v>9150.799999999999</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>447122.92</v>
+        <v>344639.5</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -8832,16 +8832,16 @@
         <v>-1.148</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>405143.33</v>
+        <v>318559.9</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>6372.9</v>
+        <v>3743.08</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-7317.04</v>
+        <v>-4297.61</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>439805.88</v>
+        <v>340341.89</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -8883,16 +8883,16 @@
         <v>2.03</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>440750.02</v>
+        <v>340896.42</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>6933</v>
+        <v>4005.53</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>14076.04</v>
+        <v>8132.42</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>453881.93</v>
+        <v>348474.31</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -8934,16 +8934,16 @@
         <v>-1.014</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>453881.93</v>
+        <v>348474.31</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>7139.56</v>
+        <v>4094.57</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>-7236.37</v>
+        <v>-4150.09</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>446645.56</v>
+        <v>344324.22</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -8985,16 +8985,16 @@
         <v>-1.014</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>446645.56</v>
+        <v>344324.22</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>7025.73</v>
+        <v>4045.81</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>-7122.64</v>
+        <v>-4101.61</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>439522.91</v>
+        <v>340222.6</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -9036,16 +9036,16 @@
         <v>-1.02</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>439619.82</v>
+        <v>340278.41</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>6915.22</v>
+        <v>3998.27</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>-7050.15</v>
+        <v>-4076.29</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>432472.76</v>
+        <v>336146.32</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9087,16 +9087,16 @@
         <v>1.138</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>432607.7</v>
+        <v>336224.33</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>6804.92</v>
+        <v>3950.64</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>7741.64</v>
+        <v>4494.46</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>440214.4</v>
+        <v>340640.77</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9138,16 +9138,16 @@
         <v>-1.082</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>425667.85</v>
+        <v>332195.68</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>6695.76</v>
+        <v>3903.3</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>-7242.35</v>
+        <v>-4221.94</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>432972.06</v>
+        <v>336418.84</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9189,16 +9189,16 @@
         <v>5.382</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>418972.09</v>
+        <v>328292.38</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>6590.43</v>
+        <v>3857.44</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>35466.96</v>
+        <v>20759.11</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>468439.02</v>
+        <v>357177.95</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9231,25 +9231,25 @@
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="G75" t="n">
         <v>0.006</v>
       </c>
       <c r="H75" t="n">
-        <v>0.926</v>
+        <v>1.094</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>412381.66</v>
+        <v>324434.95</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>6486.76</v>
+        <v>3812.11</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>6008.69</v>
+        <v>4171.97</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>474447.71</v>
+        <v>361349.93</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9291,16 +9291,16 @@
         <v>2.87</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>405894.9</v>
+        <v>320622.84</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>6384.73</v>
+        <v>3767.32</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>18321.67</v>
+        <v>10810.73</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>492769.37</v>
+        <v>372160.65</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9342,16 +9342,16 @@
         <v>4.024</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>492769.37</v>
+        <v>372160.65</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>7751.26</v>
+        <v>4372.89</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>31194.33</v>
+        <v>17598.33</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>523963.71</v>
+        <v>389758.99</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9384,25 +9384,25 @@
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1.391</v>
+        <v>1.478</v>
       </c>
       <c r="G78" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>1.304</v>
+        <v>1.391</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>485018.11</v>
+        <v>367787.77</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>7629.33</v>
+        <v>4321.51</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>9951.27</v>
+        <v>6012.7</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>533914.98</v>
+        <v>395771.69</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9444,16 +9444,16 @@
         <v>3.275</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>477388.78</v>
+        <v>363466.26</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>7509.33</v>
+        <v>4270.73</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>24594.78</v>
+        <v>13987.62</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>558509.76</v>
+        <v>409759.31</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9495,16 +9495,16 @@
         <v>-1.011</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>469879.45</v>
+        <v>359195.53</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>7391.2</v>
+        <v>4220.55</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>-7470.68</v>
+        <v>-4265.93</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>551039.08</v>
+        <v>405493.38</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9546,16 +9546,16 @@
         <v>3.097</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>462488.25</v>
+        <v>354974.98</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>7274.94</v>
+        <v>4170.96</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>22533.72</v>
+        <v>12919.3</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>573572.8</v>
+        <v>418412.68</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9597,16 +9597,16 @@
         <v>0.577</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>455213.31</v>
+        <v>350804.03</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>7160.51</v>
+        <v>4121.95</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>4130.73</v>
+        <v>2377.86</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>577703.53</v>
+        <v>420790.54</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -9648,16 +9648,16 @@
         <v>-1.048</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>577703.53</v>
+        <v>420790.54</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>9087.280000000001</v>
+        <v>4944.29</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>-9520</v>
+        <v>-5179.73</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>585896.74</v>
+        <v>425287.35</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -9699,16 +9699,16 @@
         <v>1.98</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>568616.25</v>
+        <v>415846.25</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>8944.33</v>
+        <v>4886.19</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>17713.22</v>
+        <v>9676.540000000001</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>595416.74</v>
+        <v>430467.08</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -9750,16 +9750,16 @@
         <v>1.42</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>585896.74</v>
+        <v>425287.35</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>9216.16</v>
+        <v>4997.13</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>13084.26</v>
+        <v>7094.46</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>598981</v>
+        <v>432381.81</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -9801,16 +9801,16 @@
         <v>2.123</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>598981</v>
+        <v>432381.81</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>9421.969999999999</v>
+        <v>5080.49</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>20004.93</v>
+        <v>10787</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>443168.81</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -9844,16 +9844,16 @@
         <v>-0.019</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>618985.9300000001</v>
+        <v>443168.81</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>9736.65</v>
+        <v>5207.23</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>-183.71</v>
+        <v>-98.25</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>618802.21</v>
+        <v>443070.56</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -9887,16 +9887,16 @@
         <v>-0.025</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>609249.28</v>
+        <v>437961.58</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>9583.49</v>
+        <v>5146.05</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>-239.59</v>
+        <v>-128.65</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>618562.63</v>
+        <v>442941.91</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
